--- a/Assessment Questions/AIE/PYF-110/PYTHON DATA STRUCTURES/Basic Data Structures in Python/Basic_DS.xlsx
+++ b/Assessment Questions/AIE/PYF-110/PYTHON DATA STRUCTURES/Basic Data Structures in Python/Basic_DS.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Basic_DS" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,7 +434,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -456,7 +456,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -478,7 +478,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -498,11 +498,6 @@
           <t>A) key-value B) values only C) keys only D) none</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -522,7 +517,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -544,7 +539,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -566,7 +561,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -588,7 +583,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -608,11 +603,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -630,11 +620,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -654,7 +639,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -676,7 +661,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -696,11 +681,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -720,7 +700,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -742,7 +722,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -764,7 +744,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -784,11 +764,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -808,7 +783,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -828,11 +803,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Easy</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -850,11 +820,6 @@
           <t>LeetCode-style problem</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -874,7 +839,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
